--- a/data/indicadores.xlsx
+++ b/data/indicadores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Actualizaciones web\Informes técnicos\Año 2026\16_10_26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msteren\Documents\materialesweb_2026\21102026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417273E7-0EC3-4F25-82B9-08E3D778D121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB732A8F-5DF2-4A33-B554-CC9C45074205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4CECDD37-E54E-4C33-A5DC-419B8A34BDE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{62F06117-BCCC-48EA-AD7B-B0797A5D4082}"/>
   </bookViews>
   <sheets>
     <sheet name="Principales Indicadores" sheetId="10" r:id="rId1"/>
@@ -1836,6 +1836,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -5477,7 +5478,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41590CE2-CEEA-4C72-8E7D-B2892A2C6CC7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99220382-8A93-46A7-8221-23F4B05C1DEF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5531,7 +5532,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8FD6988-E6AF-4DAE-B1D5-2B4410806BB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED5197A1-B55F-4C5B-A4F1-0A40AA906707}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5585,7 +5586,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FED5395-1901-484F-81A1-B47408F15F47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA40C4C-1E87-454D-B7A4-F75B79954820}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5639,7 +5640,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B98D4A6-7C19-42D6-A36B-95912D1448E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D5DAF8-AE2A-4ECF-A095-800F7D2D27E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5693,7 +5694,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B4833F2-EF20-4EEA-BE23-12D9186A83D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D196C892-FF64-4BA4-85AB-8A03469EC1E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5747,7 +5748,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA685CD6-17F8-48CE-A1E6-692E747200F9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F72C054C-118D-4134-A546-8F8E29CFD165}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5801,7 +5802,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5688094F-21A2-4610-94C1-C3DAEC78F91F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D375105-E18D-4D55-908C-23E0E1C6D6ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5855,7 +5856,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1160BDD3-4A23-4988-92FE-C21B6077A42D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D01B92E-E626-441A-AFB8-AECCB2619422}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5909,7 +5910,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADA220B5-59D5-465C-852C-E8C0F770A7FB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2833046D-5D5B-4D20-9A41-7074B7CF16E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6259,7 +6260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352447F2-CBEE-45F8-9870-0A6EDF448D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB8B3C0-D83E-41EC-A4FD-D20FA018E58D}">
   <sheetPr codeName="Hoja2">
     <tabColor theme="3"/>
     <pageSetUpPr fitToPage="1"/>
@@ -6273,7 +6274,7 @@
     <col min="4" max="4" width="1.44140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="116.44140625" style="4" customWidth="1"/>
     <col min="6" max="6" width="26.44140625" style="689" customWidth="1"/>
-    <col min="7" max="7" width="16" style="86" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" style="86" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="19.44140625" style="86" customWidth="1"/>
     <col min="10" max="10" width="3" style="86" customWidth="1"/>
     <col min="11" max="11" width="26.44140625" style="689" customWidth="1"/>
@@ -6377,7 +6378,7 @@
       <c r="D8" s="332"/>
       <c r="E8" s="697"/>
       <c r="F8" s="1050">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="G8" s="1050"/>
       <c r="H8" s="1050"/>
@@ -6524,20 +6525,20 @@
         <v>58</v>
       </c>
       <c r="L13" s="721">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="M13" s="722">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="N13" s="723">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="O13" s="724"/>
       <c r="P13" s="720" t="s">
         <v>58</v>
       </c>
       <c r="Q13" s="725">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="R13" s="724"/>
       <c r="S13" s="716" t="s">
@@ -6579,34 +6580,34 @@
         <v>448</v>
       </c>
       <c r="L14" s="733">
-        <v>2.1164756813683017E-2</v>
+        <v>7.1264427961461596E-3</v>
       </c>
       <c r="M14" s="61">
-        <v>7.2317311651377558E-3</v>
+        <v>3.1054066556644555E-2</v>
       </c>
       <c r="N14" s="734">
-        <v>3.1347740461844076E-2</v>
+        <v>-1.4690865441220669E-2</v>
       </c>
       <c r="O14" s="724"/>
       <c r="P14" s="1036" t="s">
         <v>240</v>
       </c>
       <c r="Q14" s="1010">
-        <v>-2.899961191920819E-2</v>
+        <v>6.5985099444598738E-4</v>
       </c>
       <c r="R14" s="724"/>
       <c r="S14" s="1047" t="s">
         <v>403</v>
       </c>
       <c r="T14" s="1010">
-        <v>-1.4417650408067084E-2</v>
+        <v>-1.7442909681778529E-2</v>
       </c>
       <c r="U14" s="1010">
-        <v>1.6597715106426048E-2</v>
+        <v>1.2379428068400866E-2</v>
       </c>
       <c r="V14" s="724"/>
       <c r="W14" s="991">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="X14" s="738"/>
     </row>
@@ -6622,13 +6623,13 @@
       <c r="J15" s="719"/>
       <c r="K15" s="1014"/>
       <c r="L15" s="744">
-        <v>-1.3572400665236906E-2</v>
+        <v>-6.4132543950433663E-3</v>
       </c>
       <c r="M15" s="745">
-        <v>-5.8713218247954391E-3</v>
+        <v>2.9746983233902569E-3</v>
       </c>
       <c r="N15" s="746">
-        <v>2.7024196757090557E-3</v>
+        <v>-2.8065440901734795E-2</v>
       </c>
       <c r="O15" s="724"/>
       <c r="P15" s="1014"/>
@@ -7150,14 +7151,14 @@
       <c r="K26" s="1029" t="s">
         <v>451</v>
       </c>
-      <c r="L26" s="763" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M26" s="759" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N26" s="760" t="e">
-        <v>#REF!</v>
+      <c r="L26" s="763">
+        <v>561015.88694743987</v>
+      </c>
+      <c r="M26" s="759">
+        <v>670215.35668045981</v>
+      </c>
+      <c r="N26" s="760">
+        <v>685446.5341880999</v>
       </c>
       <c r="O26" s="764"/>
       <c r="P26" s="1029" t="s">
@@ -7199,14 +7200,14 @@
       </c>
       <c r="J27" s="719"/>
       <c r="K27" s="1030"/>
-      <c r="L27" s="775" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M27" s="772" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N27" s="773" t="e">
-        <v>#REF!</v>
+      <c r="L27" s="775">
+        <v>0.12652733284564732</v>
+      </c>
+      <c r="M27" s="772">
+        <v>0.33082439710432121</v>
+      </c>
+      <c r="N27" s="773">
+        <v>0.13372875878902013</v>
       </c>
       <c r="O27" s="724"/>
       <c r="P27" s="1030"/>
@@ -7958,20 +7959,20 @@
         <v>58</v>
       </c>
       <c r="L43" s="721">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="M43" s="722">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="N43" s="723">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="O43" s="724"/>
       <c r="P43" s="716" t="s">
         <v>58</v>
       </c>
       <c r="Q43" s="725">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="R43" s="724"/>
       <c r="S43" s="716" t="s">
@@ -8012,35 +8013,35 @@
       <c r="K44" s="817" t="s">
         <v>141</v>
       </c>
-      <c r="L44" s="733">
-        <v>3.73E-2</v>
+      <c r="L44" s="733" t="e">
+        <v>#N/A</v>
       </c>
       <c r="M44" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="N44" s="734">
-        <v>2.8900000000000002E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
       <c r="O44" s="724"/>
       <c r="P44" s="817" t="s">
         <v>141</v>
       </c>
       <c r="Q44" s="789">
-        <v>2.8199999999999999E-2</v>
+        <v>2.7300000000000001E-2</v>
       </c>
       <c r="R44" s="724"/>
       <c r="S44" s="817" t="s">
         <v>403</v>
       </c>
       <c r="T44" s="789">
-        <v>0.36180000000000001</v>
+        <v>0.35609999999999997</v>
       </c>
       <c r="U44" s="734">
-        <v>0.21820000000000001</v>
+        <v>0.25140000000000001</v>
       </c>
       <c r="V44" s="724"/>
       <c r="W44" s="983">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="X44" s="738"/>
     </row>
@@ -8067,31 +8068,31 @@
       <c r="K45" s="822" t="s">
         <v>141</v>
       </c>
-      <c r="L45" s="823">
-        <v>0.04</v>
+      <c r="L45" s="823" t="e">
+        <v>#N/A</v>
       </c>
       <c r="M45" s="820" t="e">
         <v>#N/A</v>
       </c>
       <c r="N45" s="821">
-        <v>1.9400000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="O45" s="724"/>
       <c r="P45" s="822" t="s">
         <v>141</v>
       </c>
       <c r="Q45" s="824">
-        <v>2.2499999999999999E-2</v>
+        <v>2.8300000000000002E-2</v>
       </c>
       <c r="R45" s="724"/>
       <c r="S45" s="822" t="s">
         <v>403</v>
       </c>
       <c r="T45" s="824">
-        <v>0.29670000000000002</v>
+        <v>0.30420000000000003</v>
       </c>
       <c r="U45" s="821">
-        <v>0.1704</v>
+        <v>0.2036</v>
       </c>
       <c r="V45" s="724"/>
       <c r="W45" s="984"/>
@@ -8146,20 +8147,20 @@
         <v>58</v>
       </c>
       <c r="L47" s="721">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="M47" s="722">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="N47" s="723">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="O47" s="724"/>
       <c r="P47" s="716" t="s">
         <v>58</v>
       </c>
       <c r="Q47" s="725">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="R47" s="724"/>
       <c r="S47" s="716" t="s">
@@ -8201,34 +8202,34 @@
         <v>454</v>
       </c>
       <c r="L48" s="827">
-        <v>9577.8203815399993</v>
+        <v>9111.8498067399996</v>
       </c>
       <c r="M48" s="825">
-        <v>9111.8498067399996</v>
+        <v>8853.8595334599995</v>
       </c>
       <c r="N48" s="826">
-        <v>8853.8595334599995</v>
+        <v>8865.8847657200004</v>
       </c>
       <c r="O48" s="724"/>
       <c r="P48" s="1013" t="s">
         <v>80</v>
       </c>
       <c r="Q48" s="1022">
-        <v>67247.768785680004</v>
+        <v>10035.97518802</v>
       </c>
       <c r="R48" s="724"/>
       <c r="S48" s="1013" t="s">
         <v>403</v>
       </c>
       <c r="T48" s="1015">
-        <v>7.5091312934923398</v>
+        <v>0.23471336839141776</v>
       </c>
       <c r="U48" s="993">
-        <v>1.2671673680044098</v>
+        <v>0.21616374545680617</v>
       </c>
       <c r="V48" s="724"/>
       <c r="W48" s="1001">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="X48" s="738"/>
     </row>
@@ -8250,13 +8251,13 @@
       <c r="J49" s="719"/>
       <c r="K49" s="1014"/>
       <c r="L49" s="744">
-        <v>0.34990463382318993</v>
+        <v>0.2524430740088508</v>
       </c>
       <c r="M49" s="745">
-        <v>0.2524430740088508</v>
+        <v>0.14087958548077428</v>
       </c>
       <c r="N49" s="746">
-        <v>0.14087958548077428</v>
+        <v>0.12183614217621064</v>
       </c>
       <c r="O49" s="724"/>
       <c r="P49" s="1014"/>
@@ -8293,30 +8294,30 @@
         <v>454</v>
       </c>
       <c r="L50" s="763">
-        <v>6128.0264597900004</v>
+        <v>6876.66162343</v>
       </c>
       <c r="M50" s="759">
-        <v>6876.66162343</v>
+        <v>6755.7314468200002</v>
       </c>
       <c r="N50" s="760">
-        <v>6755.7314468200002</v>
+        <v>6706.5929163800001</v>
       </c>
       <c r="O50" s="724"/>
       <c r="P50" s="1018" t="s">
         <v>80</v>
       </c>
       <c r="Q50" s="1020">
-        <v>6695.9916438600003</v>
+        <v>7059.5011781399999</v>
       </c>
       <c r="R50" s="724"/>
       <c r="S50" s="1014" t="s">
         <v>403</v>
       </c>
       <c r="T50" s="1008">
-        <v>3.6094851246816217E-2</v>
+        <v>-1.8304803327339969E-2</v>
       </c>
       <c r="U50" s="1009">
-        <v>-2.5795771718869043E-2</v>
+        <v>-2.4674308697898328E-2</v>
       </c>
       <c r="V50" s="724"/>
       <c r="W50" s="1002"/>
@@ -8340,13 +8341,13 @@
       <c r="J51" s="719"/>
       <c r="K51" s="1014"/>
       <c r="L51" s="744">
-        <v>-3.9755587913271273E-2</v>
+        <v>-5.5478608661126638E-2</v>
       </c>
       <c r="M51" s="745">
-        <v>-5.5478608661126638E-2</v>
+        <v>7.5165456458021973E-2</v>
       </c>
       <c r="N51" s="746">
-        <v>7.5165456458021973E-2</v>
+        <v>-1.4290180255196239E-2</v>
       </c>
       <c r="O51" s="724"/>
       <c r="P51" s="1019"/>
@@ -8383,30 +8384,30 @@
         <v>80</v>
       </c>
       <c r="L52" s="833">
-        <v>3449.7939217499988</v>
+        <v>2235.1881833099997</v>
       </c>
       <c r="M52" s="830">
-        <v>2235.1881833099997</v>
+        <v>2098.1280866399993</v>
       </c>
       <c r="N52" s="831">
-        <v>2098.1280866399993</v>
+        <v>2159.2918493400002</v>
       </c>
       <c r="O52" s="724"/>
       <c r="P52" s="832" t="s">
         <v>80</v>
       </c>
       <c r="Q52" s="834">
-        <v>60551.777141820006</v>
+        <v>2976.4740098800003</v>
       </c>
       <c r="R52" s="724"/>
       <c r="S52" s="832" t="s">
         <v>80</v>
       </c>
       <c r="T52" s="831">
-        <v>60551.777141820006</v>
+        <v>2976.4740098800003</v>
       </c>
       <c r="U52" s="831">
-        <v>76614.264867329999</v>
+        <v>21198.253584729995</v>
       </c>
       <c r="V52" s="724"/>
       <c r="W52" s="1003"/>
@@ -8680,14 +8681,14 @@
       <c r="K59" s="859" t="s">
         <v>63</v>
       </c>
-      <c r="L59" s="860" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M59" s="861" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N59" s="862" t="e">
-        <v>#REF!</v>
+      <c r="L59" s="860">
+        <v>394.35600000000011</v>
+      </c>
+      <c r="M59" s="861">
+        <v>382.89800000000002</v>
+      </c>
+      <c r="N59" s="862">
+        <v>313.36500000000018</v>
       </c>
       <c r="O59" s="764"/>
       <c r="P59" s="1007" t="s">
@@ -8732,14 +8733,14 @@
       <c r="K60" s="870" t="s">
         <v>67</v>
       </c>
-      <c r="L60" s="871" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M60" s="846" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N60" s="869" t="e">
-        <v>#REF!</v>
+      <c r="L60" s="871">
+        <v>7.6005457025921208E-2</v>
+      </c>
+      <c r="M60" s="846">
+        <v>-3.163131682603737E-3</v>
+      </c>
+      <c r="N60" s="869">
+        <v>-0.14637468366843776</v>
       </c>
       <c r="O60" s="724"/>
       <c r="P60" s="1007"/>
@@ -8776,14 +8777,14 @@
       <c r="K61" s="859" t="s">
         <v>63</v>
       </c>
-      <c r="L61" s="860" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M61" s="861" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N61" s="862" t="e">
-        <v>#REF!</v>
+      <c r="L61" s="860">
+        <v>239.68199999999979</v>
+      </c>
+      <c r="M61" s="861">
+        <v>205.077</v>
+      </c>
+      <c r="N61" s="862">
+        <v>185.87299999999988</v>
       </c>
       <c r="O61" s="724"/>
       <c r="P61" s="1007" t="s">
@@ -8828,14 +8829,14 @@
       <c r="K62" s="870" t="s">
         <v>67</v>
       </c>
-      <c r="L62" s="871" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M62" s="846" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N62" s="869" t="e">
-        <v>#REF!</v>
+      <c r="L62" s="871">
+        <v>0.26709946182556288</v>
+      </c>
+      <c r="M62" s="846">
+        <v>0.25358819502176155</v>
+      </c>
+      <c r="N62" s="869">
+        <v>0.13174334494264284</v>
       </c>
       <c r="O62" s="724"/>
       <c r="P62" s="1007"/>
@@ -8872,14 +8873,14 @@
       <c r="K63" s="873" t="s">
         <v>63</v>
       </c>
-      <c r="L63" s="860" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M63" s="861" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N63" s="862" t="e">
-        <v>#REF!</v>
+      <c r="L63" s="860">
+        <v>-154.67400000000032</v>
+      </c>
+      <c r="M63" s="861">
+        <v>-177.82100000000003</v>
+      </c>
+      <c r="N63" s="862">
+        <v>-127.4920000000003</v>
       </c>
       <c r="O63" s="724"/>
       <c r="P63" s="873" t="s">
@@ -9576,28 +9577,28 @@
       <c r="K79" s="886" t="s">
         <v>424</v>
       </c>
-      <c r="L79" s="806" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M79" s="730" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N79" s="731" t="e">
-        <v>#REF!</v>
+      <c r="L79" s="806">
+        <v>0.20484312535475308</v>
+      </c>
+      <c r="M79" s="730">
+        <v>0.16623821471133188</v>
+      </c>
+      <c r="N79" s="731">
+        <v>0.10466575907109034</v>
       </c>
       <c r="O79" s="724"/>
       <c r="P79" s="886" t="s">
         <v>424</v>
       </c>
-      <c r="Q79" s="735" t="e">
-        <v>#REF!</v>
+      <c r="Q79" s="735">
+        <v>0.13167356832653845</v>
       </c>
       <c r="R79" s="724"/>
       <c r="S79" s="886" t="s">
         <v>425</v>
       </c>
-      <c r="T79" s="887" t="e">
-        <v>#REF!</v>
+      <c r="T79" s="887">
+        <v>-2.4050790574170646</v>
       </c>
       <c r="U79" s="883"/>
       <c r="V79" s="724"/>
@@ -9864,28 +9865,28 @@
       <c r="K85" s="889" t="s">
         <v>433</v>
       </c>
-      <c r="L85" s="911" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M85" s="909" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N85" s="910" t="e">
-        <v>#N/A</v>
+      <c r="L85" s="911">
+        <v>36116.317146624169</v>
+      </c>
+      <c r="M85" s="909">
+        <v>35968.922650438151</v>
+      </c>
+      <c r="N85" s="910">
+        <v>33605.132817114958</v>
       </c>
       <c r="O85" s="764"/>
       <c r="P85" s="889" t="s">
         <v>433</v>
       </c>
-      <c r="Q85" s="776" t="e">
-        <v>#REF!</v>
+      <c r="Q85" s="776">
+        <v>34033.881635953992</v>
       </c>
       <c r="R85" s="764"/>
       <c r="S85" s="892" t="s">
         <v>403</v>
       </c>
-      <c r="T85" s="912" t="e">
-        <v>#REF!</v>
+      <c r="T85" s="912">
+        <v>1.1606931131371345E-2</v>
       </c>
       <c r="U85" s="883"/>
       <c r="V85" s="724"/>
@@ -10226,14 +10227,14 @@
       <c r="K93" s="927" t="s">
         <v>67</v>
       </c>
-      <c r="L93" s="840" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="M93" s="838" t="e">
-        <v>#REF!</v>
-      </c>
-      <c r="N93" s="839" t="e">
-        <v>#REF!</v>
+      <c r="L93" s="840">
+        <v>5.129969871082074E-2</v>
+      </c>
+      <c r="M93" s="838">
+        <v>-1.070812606270477E-2</v>
+      </c>
+      <c r="N93" s="839">
+        <v>-3.6337922306362014E-4</v>
       </c>
       <c r="O93" s="764"/>
       <c r="P93" s="774" t="s">
@@ -11229,14 +11230,14 @@
     <mergeCell ref="W103:W104"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G2" location="Sectores!A1" display="Sectorial" xr:uid="{E8C5DF06-ABD8-4A3E-B867-2DF7AE786211}"/>
-    <hyperlink ref="I2" location="'Empleo y Condiciones de Vida'!A1" display="Empleo" xr:uid="{00578A08-742E-4A19-9004-6FA1BF952CC6}"/>
-    <hyperlink ref="L2" location="'Sector Externo'!A1" display="Sector Externo" xr:uid="{457B83E7-6AEA-4051-AF15-90982C76F9D2}"/>
-    <hyperlink ref="M2" location="'Turismo y servicios'!A1" display="Turismo y Servicios" xr:uid="{6B5AF0A5-5B4D-47B3-94F0-3B61FEC45AC3}"/>
-    <hyperlink ref="K2" location="'Precios y Canastas'!A1" display="Precios" xr:uid="{7717BAEE-9B06-4024-8E8D-EA7122917401}"/>
-    <hyperlink ref="H2" location="Comercio!A1" display="Comercio" xr:uid="{C9AD540F-622A-44C0-9CF3-259F40F41441}"/>
-    <hyperlink ref="Q2" location="Fuentes!A1" display="Fuentes" xr:uid="{0F86CFA2-2AC2-4A49-8E36-7219409AF640}"/>
-    <hyperlink ref="F2" location="'Cuentas Nacionales'!A1" display="Cuentas Nacionales" xr:uid="{F4A21DC1-DE51-45C2-84B3-FDC086957372}"/>
+    <hyperlink ref="G2" location="Sectores!A1" display="Sectorial" xr:uid="{3244D3F3-E503-4B4E-A4FF-202F194B4AAA}"/>
+    <hyperlink ref="I2" location="'Empleo y Condiciones de Vida'!A1" display="Empleo" xr:uid="{32CD046C-120E-40C7-8CA4-7F84BEF9C092}"/>
+    <hyperlink ref="L2" location="'Sector Externo'!A1" display="Sector Externo" xr:uid="{6563D6DD-279E-48EA-B43C-0366600ACE3C}"/>
+    <hyperlink ref="M2" location="'Turismo y servicios'!A1" display="Turismo y Servicios" xr:uid="{B13B4E21-369E-49D8-BAD5-2CF3AF4A97EE}"/>
+    <hyperlink ref="K2" location="'Precios y Canastas'!A1" display="Precios" xr:uid="{056ED8DF-7B52-4F82-A410-DC4323B6C20C}"/>
+    <hyperlink ref="H2" location="Comercio!A1" display="Comercio" xr:uid="{49D5AA4E-C650-49F2-A181-2A1B67B1C548}"/>
+    <hyperlink ref="Q2" location="Fuentes!A1" display="Fuentes" xr:uid="{E62321A6-BE8B-4BF8-8467-2DCE43E95046}"/>
+    <hyperlink ref="F2" location="'Cuentas Nacionales'!A1" display="Cuentas Nacionales" xr:uid="{6EB1D248-EC0C-4401-96CC-189135B14CF2}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.59055118110236227" bottom="0.39370078740157483" header="1.5748031496062993" footer="1.1811023622047245"/>
   <pageSetup scale="19" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -11245,7 +11246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83300159-BB23-4B38-84C0-5F2B39F3C333}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2DFABF-64E5-48F1-9DC3-268A55179E88}">
   <sheetPr codeName="Hoja3">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11335,7 +11336,7 @@
       <c r="K11" s="97"/>
       <c r="L11" s="97"/>
       <c r="N11" s="1058">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="O11" s="1071"/>
       <c r="P11" s="1059"/>
@@ -11360,13 +11361,13 @@
         <v>58</v>
       </c>
       <c r="J12" s="104">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="K12" s="105">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="L12" s="106">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="N12" s="196" t="s">
         <v>240</v>
@@ -11419,23 +11420,23 @@
         <v>449</v>
       </c>
       <c r="J14" s="425">
-        <v>2.1164756813683017E-2</v>
+        <v>7.1264427961461596E-3</v>
       </c>
       <c r="K14" s="426">
-        <v>7.2317311651377558E-3</v>
+        <v>3.1054066556644555E-2</v>
       </c>
       <c r="L14" s="427">
-        <v>3.1347740461844076E-2</v>
+        <v>-1.4690865441220669E-2</v>
       </c>
       <c r="M14" s="324"/>
       <c r="N14" s="1063">
-        <v>-2.899961191920819E-2</v>
+        <v>6.5985099444598738E-4</v>
       </c>
       <c r="O14" s="1065">
-        <v>-1.4417650408067084E-2</v>
+        <v>-1.7442909681778529E-2</v>
       </c>
       <c r="P14" s="1064">
-        <v>1.6597715106426048E-2</v>
+        <v>1.2379428068400866E-2</v>
       </c>
       <c r="Q14" s="271"/>
     </row>
@@ -11449,13 +11450,13 @@
       <c r="H15" s="567"/>
       <c r="I15" s="1075"/>
       <c r="J15" s="363">
-        <v>-1.3572400665236906E-2</v>
+        <v>-6.4132543950433663E-3</v>
       </c>
       <c r="K15" s="361">
-        <v>-5.8713218247954391E-3</v>
+        <v>2.9746983233902569E-3</v>
       </c>
       <c r="L15" s="364">
-        <v>2.7024196757090557E-3</v>
+        <v>-2.8065440901734795E-2</v>
       </c>
       <c r="M15" s="568"/>
       <c r="N15" s="1076"/>
@@ -11485,23 +11486,23 @@
         <v>67</v>
       </c>
       <c r="J16" s="358">
-        <v>0.11369768298714811</v>
+        <v>4.752783574028796E-2</v>
       </c>
       <c r="K16" s="359">
-        <v>4.7721480925332793E-2</v>
+        <v>5.0746981146259085E-2</v>
       </c>
       <c r="L16" s="360">
-        <v>5.2979239333568851E-2</v>
+        <v>1.0172522438729015E-2</v>
       </c>
       <c r="M16" s="362"/>
       <c r="N16" s="358" t="s">
         <v>244</v>
       </c>
       <c r="O16" s="359">
-        <v>6.5214228815286823E-3</v>
+        <v>-1.012414920803939E-2</v>
       </c>
       <c r="P16" s="360">
-        <v>9.819894928684314E-2</v>
+        <v>9.1538629690274709E-2</v>
       </c>
       <c r="Q16" s="230"/>
       <c r="R16" s="531"/>
@@ -11525,23 +11526,23 @@
       <c r="H17" s="361"/>
       <c r="I17" s="1056"/>
       <c r="J17" s="363">
-        <v>-0.19743030580678433</v>
+        <v>-0.2019192704480901</v>
       </c>
       <c r="K17" s="361">
-        <v>-0.20192146141610023</v>
+        <v>2.5011507260088055</v>
       </c>
       <c r="L17" s="364">
-        <v>2.5011693239395636</v>
+        <v>4.245038682823731</v>
       </c>
       <c r="M17" s="362"/>
       <c r="N17" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O17" s="361">
-        <v>4.2451175556314471</v>
+        <v>-0.15696061213720003</v>
       </c>
       <c r="P17" s="364">
-        <v>0.65797224734986592</v>
+        <v>0.47025433780779635</v>
       </c>
       <c r="Q17" s="230"/>
       <c r="R17" s="531"/>
@@ -11565,23 +11566,23 @@
       <c r="H18" s="361"/>
       <c r="I18" s="1056"/>
       <c r="J18" s="363">
-        <v>0.17131641799435804</v>
+        <v>0.16203720668146415</v>
       </c>
       <c r="K18" s="361">
-        <v>0.16204098043907234</v>
+        <v>0.15798614886287687</v>
       </c>
       <c r="L18" s="364">
-        <v>0.15799193655054999</v>
+        <v>8.8939689127241373E-2</v>
       </c>
       <c r="M18" s="362"/>
       <c r="N18" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O18" s="361">
-        <v>8.4299692832629392E-2</v>
+        <v>0.11116792857500446</v>
       </c>
       <c r="P18" s="364">
-        <v>0.13489831052045465</v>
+        <v>0.13239493026107207</v>
       </c>
       <c r="Q18" s="230"/>
       <c r="R18" s="531"/>
@@ -11605,23 +11606,23 @@
       <c r="H19" s="361"/>
       <c r="I19" s="1056"/>
       <c r="J19" s="363">
-        <v>-2.6028535671957953E-2</v>
+        <v>-5.5861993797851284E-2</v>
       </c>
       <c r="K19" s="361">
-        <v>-5.6077073822758949E-2</v>
+        <v>1.9144180482427053E-2</v>
       </c>
       <c r="L19" s="364">
-        <v>1.9664382455252261E-2</v>
+        <v>-4.612986452665635E-2</v>
       </c>
       <c r="M19" s="362"/>
       <c r="N19" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O19" s="361">
-        <v>-4.5801869129427075E-2</v>
+        <v>-3.2406652261254054E-2</v>
       </c>
       <c r="P19" s="364">
-        <v>-2.3802280440468948E-2</v>
+        <v>-2.4975726108651064E-2</v>
       </c>
       <c r="Q19" s="230"/>
       <c r="R19" s="531"/>
@@ -11634,10 +11635,10 @@
       </c>
       <c r="D20" s="1056"/>
       <c r="E20" s="553">
-        <v>-6.9267501040267687E-3</v>
+        <v>-6.9267501040253254E-3</v>
       </c>
       <c r="F20" s="397">
-        <v>1.0490878700226691E-3</v>
+        <v>1.0490878700217809E-3</v>
       </c>
       <c r="G20" s="398">
         <v>6.8179200796953943E-3</v>
@@ -11645,23 +11646,23 @@
       <c r="H20" s="361"/>
       <c r="I20" s="1056"/>
       <c r="J20" s="363">
-        <v>7.0521877443131986E-2</v>
+        <v>9.0820646355106449E-2</v>
       </c>
       <c r="K20" s="361">
-        <v>9.0887326146606107E-2</v>
+        <v>-2.6096307186188605E-3</v>
       </c>
       <c r="L20" s="364">
-        <v>-3.0398483715899927E-3</v>
+        <v>2.4463215966593621E-2</v>
       </c>
       <c r="M20" s="362"/>
       <c r="N20" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O20" s="361">
-        <v>1.8953943072517188E-2</v>
+        <v>4.2993286061239422E-2</v>
       </c>
       <c r="P20" s="364">
-        <v>1.9034411752352209E-2</v>
+        <v>2.2755001366200345E-2</v>
       </c>
       <c r="Q20" s="230"/>
       <c r="R20" s="531"/>
@@ -11685,23 +11686,23 @@
       <c r="H21" s="361"/>
       <c r="I21" s="1056"/>
       <c r="J21" s="363">
-        <v>-2.0953185643046046E-2</v>
+        <v>1.6919170275041306E-2</v>
       </c>
       <c r="K21" s="361">
-        <v>1.6750601710118218E-2</v>
+        <v>1.39445667136604E-2</v>
       </c>
       <c r="L21" s="364">
-        <v>1.3016268455012359E-2</v>
+        <v>-2.7212666616834524E-2</v>
       </c>
       <c r="M21" s="362"/>
       <c r="N21" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O21" s="361">
-        <v>-3.2764084947522698E-2</v>
+        <v>-2.5454270645028587E-2</v>
       </c>
       <c r="P21" s="364">
-        <v>6.710900550629173E-3</v>
+        <v>3.2048763545777792E-3</v>
       </c>
       <c r="Q21" s="230"/>
       <c r="R21" s="531"/>
@@ -11725,23 +11726,23 @@
       <c r="H22" s="361"/>
       <c r="I22" s="1056"/>
       <c r="J22" s="363">
-        <v>-9.9185041643831129E-3</v>
+        <v>-1.9565068347622505E-2</v>
       </c>
       <c r="K22" s="361">
-        <v>-1.9680390458013841E-2</v>
+        <v>3.1792009148209566E-2</v>
       </c>
       <c r="L22" s="364">
-        <v>3.2030575900195313E-2</v>
+        <v>-5.0388070041845645E-2</v>
       </c>
       <c r="M22" s="362"/>
       <c r="N22" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O22" s="361">
-        <v>-5.0541146327714892E-2</v>
+        <v>-3.4984163944640878E-2</v>
       </c>
       <c r="P22" s="364">
-        <v>-7.1131336166320169E-3</v>
+        <v>-1.0531944329457033E-2</v>
       </c>
       <c r="Q22" s="230"/>
       <c r="R22" s="531"/>
@@ -11765,23 +11766,23 @@
       <c r="H23" s="361"/>
       <c r="I23" s="1056"/>
       <c r="J23" s="363">
-        <v>2.3899078565483789E-2</v>
+        <v>2.1418409110101955E-2</v>
       </c>
       <c r="K23" s="361">
-        <v>2.1447127925759979E-2</v>
+        <v>1.0493237086860008E-2</v>
       </c>
       <c r="L23" s="364">
-        <v>7.3967455438668228E-3</v>
+        <v>3.4409586194592556E-2</v>
       </c>
       <c r="M23" s="362"/>
       <c r="N23" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O23" s="361">
-        <v>2.4636585471690342E-2</v>
+        <v>3.0712196799509428E-2</v>
       </c>
       <c r="P23" s="364">
-        <v>2.297375067749563E-2</v>
+        <v>2.5212504621783705E-2</v>
       </c>
       <c r="Q23" s="230"/>
       <c r="R23" s="531"/>
@@ -11805,23 +11806,23 @@
       <c r="H24" s="361"/>
       <c r="I24" s="1056"/>
       <c r="J24" s="363">
-        <v>2.2230059176173045E-2</v>
+        <v>9.1295609154786739E-3</v>
       </c>
       <c r="K24" s="361">
-        <v>9.3204358320877478E-3</v>
+        <v>1.7104382012278263E-2</v>
       </c>
       <c r="L24" s="364">
-        <v>1.728186635983886E-2</v>
+        <v>-2.278141642185938E-2</v>
       </c>
       <c r="M24" s="362"/>
       <c r="N24" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O24" s="361">
-        <v>-1.4625697267290461E-2</v>
+        <v>-2.8758814541252731E-2</v>
       </c>
       <c r="P24" s="364">
-        <v>1.4170673871121142E-2</v>
+        <v>7.8280126980170284E-3</v>
       </c>
       <c r="Q24" s="230"/>
       <c r="R24" s="531"/>
@@ -11845,23 +11846,23 @@
       <c r="H25" s="361"/>
       <c r="I25" s="1056"/>
       <c r="J25" s="363">
-        <v>5.4798628884680234E-2</v>
+        <v>2.7567891112115106E-2</v>
       </c>
       <c r="K25" s="361">
-        <v>2.7458223357713862E-2</v>
+        <v>6.0926387965920981E-2</v>
       </c>
       <c r="L25" s="364">
-        <v>6.0954588753626027E-2</v>
+        <v>-3.065213319700133E-2</v>
       </c>
       <c r="M25" s="362"/>
       <c r="N25" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O25" s="361">
-        <v>-3.0480308296247927E-2</v>
+        <v>-3.8156592062511763E-2</v>
       </c>
       <c r="P25" s="364">
-        <v>4.6034073332752223E-2</v>
+        <v>3.4690346991228305E-2</v>
       </c>
       <c r="Q25" s="230"/>
       <c r="R25" s="531"/>
@@ -11885,23 +11886,23 @@
       <c r="H26" s="361"/>
       <c r="I26" s="1056"/>
       <c r="J26" s="363">
-        <v>5.1311406515730518E-4</v>
+        <v>4.1613183093316408E-3</v>
       </c>
       <c r="K26" s="361">
-        <v>4.2883052371860408E-3</v>
+        <v>1.5581274687792357E-2</v>
       </c>
       <c r="L26" s="364">
-        <v>1.5561858096462933E-2</v>
+        <v>-7.4704208467957223E-4</v>
       </c>
       <c r="M26" s="362"/>
       <c r="N26" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O26" s="361">
-        <v>2.2161061851599939E-4</v>
+        <v>4.2343899227414994E-3</v>
       </c>
       <c r="P26" s="364">
-        <v>6.729048563374862E-3</v>
+        <v>6.2923816056099646E-3</v>
       </c>
       <c r="Q26" s="230"/>
       <c r="R26" s="531"/>
@@ -11925,23 +11926,23 @@
       <c r="H27" s="361"/>
       <c r="I27" s="1056"/>
       <c r="J27" s="363">
-        <v>-1.3830033336224345E-2</v>
+        <v>-1.4059441081554769E-2</v>
       </c>
       <c r="K27" s="361">
-        <v>-1.4059441081554769E-2</v>
+        <v>-1.5300983211133268E-2</v>
       </c>
       <c r="L27" s="364">
-        <v>-1.5300983211133268E-2</v>
+        <v>-1.6279877026603939E-2</v>
       </c>
       <c r="M27" s="362"/>
       <c r="N27" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O27" s="361">
-        <v>-1.4581011226172946E-2</v>
+        <v>-1.6498522503940682E-2</v>
       </c>
       <c r="P27" s="364">
-        <v>-1.4179712004113387E-2</v>
+        <v>-1.4679969922212877E-2</v>
       </c>
       <c r="Q27" s="230"/>
       <c r="R27" s="531"/>
@@ -11965,23 +11966,23 @@
       <c r="H28" s="361"/>
       <c r="I28" s="1056"/>
       <c r="J28" s="363">
-        <v>9.5653613370272339E-4</v>
+        <v>1.2613893201067761E-3</v>
       </c>
       <c r="K28" s="361">
-        <v>1.191454534004821E-3</v>
+        <v>1.0196255996246517E-3</v>
       </c>
       <c r="L28" s="364">
-        <v>1.3503285731324421E-3</v>
+        <v>-1.3677750239696751E-3</v>
       </c>
       <c r="M28" s="362"/>
       <c r="N28" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O28" s="361">
-        <v>-6.9385365873464444E-4</v>
+        <v>-3.3050229494543393E-3</v>
       </c>
       <c r="P28" s="364">
-        <v>1.0070697586432864E-3</v>
+        <v>3.7641106878361086E-4</v>
       </c>
       <c r="Q28" s="229"/>
       <c r="R28" s="533"/>
@@ -12005,23 +12006,23 @@
       <c r="H29" s="361"/>
       <c r="I29" s="1056"/>
       <c r="J29" s="363">
-        <v>3.717860189619282E-3</v>
+        <v>4.1073461520879651E-3</v>
       </c>
       <c r="K29" s="361">
-        <v>3.7256019071059132E-3</v>
+        <v>5.8969861985962435E-3</v>
       </c>
       <c r="L29" s="364">
-        <v>6.4400813490275155E-3</v>
+        <v>1.923183458633515E-3</v>
       </c>
       <c r="M29" s="362"/>
       <c r="N29" s="363" t="s">
         <v>244</v>
       </c>
       <c r="O29" s="361">
-        <v>9.9590712544752602E-3</v>
+        <v>5.5132052803132936E-3</v>
       </c>
       <c r="P29" s="364">
-        <v>4.9861257620980037E-3</v>
+        <v>4.0680894897722197E-3</v>
       </c>
       <c r="Q29" s="229"/>
       <c r="R29" s="533"/>
@@ -12045,23 +12046,23 @@
       <c r="H30" s="361"/>
       <c r="I30" s="1060"/>
       <c r="J30" s="472">
-        <v>-1.7964180983128575E-2</v>
+        <v>-1.4416790219222486E-2</v>
       </c>
       <c r="K30" s="473">
-        <v>-1.3040649416930838E-2</v>
+        <v>4.4098059003871981E-4</v>
       </c>
       <c r="L30" s="474">
-        <v>4.2236334875260795E-3</v>
+        <v>-1.224030456638614E-2</v>
       </c>
       <c r="M30" s="362"/>
       <c r="N30" s="472" t="s">
         <v>244</v>
       </c>
       <c r="O30" s="473">
-        <v>-1.3164066079005554E-2</v>
+        <v>-5.5595217298139987E-3</v>
       </c>
       <c r="P30" s="474">
-        <v>-2.4480131134861915E-3</v>
+        <v>-2.7077764986638275E-3</v>
       </c>
       <c r="Q30" s="229"/>
       <c r="R30" s="533"/>
@@ -12090,23 +12091,23 @@
         <v>67</v>
       </c>
       <c r="J31" s="368">
-        <v>2.3971616804806084E-2</v>
+        <v>9.3847905705051193E-3</v>
       </c>
       <c r="K31" s="369">
-        <v>9.9476223376768758E-3</v>
+        <v>2.1195477211379377E-2</v>
       </c>
       <c r="L31" s="370">
-        <v>2.0790178107495283E-2</v>
+        <v>-4.5062055622317132E-2</v>
       </c>
       <c r="M31" s="510"/>
       <c r="N31" s="368" t="s">
         <v>244</v>
       </c>
       <c r="O31" s="369">
-        <v>-4.5143768369421799E-2</v>
+        <v>-4.2053256669804862E-2</v>
       </c>
       <c r="P31" s="370">
-        <v>8.0544105862312421E-3</v>
+        <v>1.5520960399837413E-3</v>
       </c>
       <c r="Q31" s="139"/>
       <c r="R31" s="536"/>
@@ -13938,8 +13939,8 @@
     <mergeCell ref="I67:I68"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{F2F3C945-400B-4A4B-A728-5CC64A75D4F8}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{F4B65F9D-4D75-4CE2-9C49-A049A54B76EF}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{DB667868-834F-43FC-ADA4-8725B3930300}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{ACF46E43-5AF0-48E8-BB6C-D7014FF0F7E5}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="37" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13948,7 +13949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185BA43B-C7E3-41E3-8694-8E3349F6F4F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8DBD80-F0E8-4A2E-BC38-3D024831FEB1}">
   <sheetPr codeName="Hoja5">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -17137,8 +17138,8 @@
     <mergeCell ref="N74:P74"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{3FA8AAE7-C98D-42A0-94AC-A9AB7288BBD5}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{8678169F-5FF8-405E-8113-FC8F98F37856}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{A95F10C0-8B8B-4D86-A59A-893C6F837BD2}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{B673D561-2864-425D-8085-B1F35532FA5F}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="39" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -17147,7 +17148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28807275-614F-49E0-BB3B-80A5D8E76BAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B16215-9F64-4E12-9ABB-FF9768DED4AD}">
   <sheetPr codeName="Hoja4">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -20308,9 +20309,9 @@
     <mergeCell ref="N78:P78"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K1" location="TABLERO!Área_de_impresión" display="Tablero general" xr:uid="{06399B57-98B0-47BF-93CE-B96AA2B46C5C}"/>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{E8481E5D-DFFC-422C-9D74-F8B5459F750E}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{9689FD04-42EB-4DE2-8296-DC41A2CB1672}"/>
+    <hyperlink ref="K1" location="TABLERO!Área_de_impresión" display="Tablero general" xr:uid="{BE23A896-D8AC-453E-8EC7-E23293DF782C}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{DDAE3DA5-F141-41F5-A932-CA1434AFB11B}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{8155C951-71AF-4879-95EF-B7C2106C2312}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="39" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20319,7 +20320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51A9977-F7BE-4726-94A6-AAEDC0C8A702}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56151739-16AC-4A39-9452-4B35CB0A840B}">
   <sheetPr codeName="Hoja7">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -23180,8 +23181,8 @@
     <mergeCell ref="N85:P85"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{8DE674B4-E71C-49A6-91B2-EC3764EFBFD2}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{BA0E49A9-E8B9-485D-8FC0-3EAD7A6577AD}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{63995F9F-412C-45C0-8E26-9BFB3572C975}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{39B30AF8-77E0-4CC3-AEC5-79A541C93BEB}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="38" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23190,7 +23191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E6E32-8D29-4B29-8FD5-57019A2B9CA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5F825F-CC1B-4807-9B0A-2DA80E81DB84}">
   <sheetPr codeName="Hoja6">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -23378,7 +23379,7 @@
       <c r="L11" s="97"/>
       <c r="M11" s="95"/>
       <c r="N11" s="1115">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="O11" s="1116"/>
       <c r="P11" s="1117"/>
@@ -23405,13 +23406,13 @@
         <v>58</v>
       </c>
       <c r="J12" s="104">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="K12" s="105">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="L12" s="106">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="M12" s="255"/>
       <c r="N12" s="340" t="s">
@@ -23468,24 +23469,24 @@
       <c r="I14" s="348" t="s">
         <v>141</v>
       </c>
-      <c r="J14" s="348">
-        <v>3.73E-2</v>
+      <c r="J14" s="348" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K14" s="349" t="e">
         <v>#N/A</v>
       </c>
       <c r="L14" s="350">
-        <v>2.8900000000000002E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
       <c r="M14" s="351"/>
       <c r="N14" s="352">
-        <v>2.8199999999999999E-2</v>
+        <v>2.7300000000000001E-2</v>
       </c>
       <c r="O14" s="353">
-        <v>0.21820000000000001</v>
+        <v>0.25140000000000001</v>
       </c>
       <c r="P14" s="354">
-        <v>0.36180000000000001</v>
+        <v>0.35609999999999997</v>
       </c>
       <c r="Q14" s="271"/>
     </row>
@@ -23511,24 +23512,24 @@
       <c r="I15" s="1061" t="s">
         <v>141</v>
       </c>
-      <c r="J15" s="358">
-        <v>3.4500000000000003E-2</v>
+      <c r="J15" s="358" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K15" s="359" t="e">
         <v>#N/A</v>
       </c>
       <c r="L15" s="360">
-        <v>2.4199999999999999E-2</v>
+        <v>2.4900000000000002E-2</v>
       </c>
       <c r="M15" s="362"/>
       <c r="N15" s="363">
-        <v>2.4900000000000002E-2</v>
+        <v>2.64E-2</v>
       </c>
       <c r="O15" s="361">
-        <v>0.18340000000000001</v>
+        <v>0.21460000000000001</v>
       </c>
       <c r="P15" s="364">
-        <v>0.30099999999999999</v>
+        <v>0.30380000000000001</v>
       </c>
       <c r="Q15" s="230"/>
     </row>
@@ -23550,24 +23551,24 @@
       </c>
       <c r="H16" s="361"/>
       <c r="I16" s="1056"/>
-      <c r="J16" s="363">
-        <v>0.04</v>
+      <c r="J16" s="363" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K16" s="361" t="e">
         <v>#N/A</v>
       </c>
       <c r="L16" s="364">
-        <v>1.9400000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="M16" s="362"/>
       <c r="N16" s="363">
-        <v>2.2499999999999999E-2</v>
+        <v>2.8300000000000002E-2</v>
       </c>
       <c r="O16" s="361">
-        <v>0.1704</v>
+        <v>0.2036</v>
       </c>
       <c r="P16" s="364">
-        <v>0.29670000000000002</v>
+        <v>0.30420000000000003</v>
       </c>
       <c r="Q16" s="230"/>
     </row>
@@ -23589,24 +23590,24 @@
       </c>
       <c r="H17" s="361"/>
       <c r="I17" s="1056"/>
-      <c r="J17" s="363">
-        <v>2.3300000000000001E-2</v>
+      <c r="J17" s="363" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K17" s="361" t="e">
         <v>#N/A</v>
       </c>
       <c r="L17" s="364">
-        <v>3.4200000000000001E-2</v>
+        <v>2.9700000000000001E-2</v>
       </c>
       <c r="M17" s="362"/>
       <c r="N17" s="363">
-        <v>2.9700000000000001E-2</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="O17" s="361">
-        <v>0.21059999999999998</v>
+        <v>0.2379</v>
       </c>
       <c r="P17" s="364">
-        <v>0.30990000000000001</v>
+        <v>0.30309999999999998</v>
       </c>
       <c r="Q17" s="230"/>
     </row>
@@ -23628,24 +23629,24 @@
       </c>
       <c r="H18" s="361"/>
       <c r="I18" s="1057"/>
-      <c r="J18" s="368">
-        <v>4.6900000000000004E-2</v>
+      <c r="J18" s="368" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K18" s="369" t="e">
         <v>#N/A</v>
       </c>
       <c r="L18" s="370">
-        <v>4.4299999999999999E-2</v>
+        <v>3.8900000000000004E-2</v>
       </c>
       <c r="M18" s="362"/>
       <c r="N18" s="368">
-        <v>3.8900000000000004E-2</v>
+        <v>0.03</v>
       </c>
       <c r="O18" s="369">
-        <v>0.34409999999999996</v>
+        <v>0.38439999999999996</v>
       </c>
       <c r="P18" s="370">
-        <v>0.59939999999999993</v>
+        <v>0.55359999999999998</v>
       </c>
       <c r="Q18" s="230"/>
     </row>
@@ -26193,8 +26194,8 @@
     <mergeCell ref="I78:I81"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{792A5F89-74AE-4735-9699-7590CE71BC1D}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{082ED878-BB6F-4357-B13D-C9CB99998480}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{15F3119D-1044-4FB7-ABE2-50ED3FBF1377}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{13CD863A-87F4-459A-BCD6-57B539AB05E6}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="40" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -26203,7 +26204,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3070E45E-FB3F-4FC9-A118-2F794D825AB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60C285F-861D-4B03-89FF-A548A270654A}">
   <sheetPr codeName="Hoja8">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -26381,7 +26382,7 @@
       <c r="L11" s="97"/>
       <c r="M11" s="95"/>
       <c r="N11" s="1058">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="O11" s="1059"/>
       <c r="P11" s="95"/>
@@ -26407,13 +26408,13 @@
         <v>58</v>
       </c>
       <c r="J12" s="104">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="K12" s="105">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="L12" s="106">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="M12" s="255"/>
       <c r="N12" s="107" t="s">
@@ -26489,20 +26490,20 @@
         <v>80</v>
       </c>
       <c r="J15" s="129">
-        <v>9577.8203815399993</v>
+        <v>9111.8498067399996</v>
       </c>
       <c r="K15" s="130">
-        <v>9111.8498067399996</v>
+        <v>8853.8595334599995</v>
       </c>
       <c r="L15" s="131">
-        <v>8853.8595334599995</v>
+        <v>8865.8847657200004</v>
       </c>
       <c r="M15" s="75"/>
       <c r="N15" s="129">
-        <v>67247.768785680004</v>
+        <v>10035.97518802</v>
       </c>
       <c r="O15" s="131">
-        <v>125612.95507259</v>
+        <v>77267.046240650001</v>
       </c>
       <c r="P15" s="258"/>
       <c r="Q15" s="229"/>
@@ -26528,20 +26529,20 @@
         <v>67</v>
       </c>
       <c r="J16" s="232">
-        <v>0.34990463382318993</v>
+        <v>0.2524430740088508</v>
       </c>
       <c r="K16" s="233">
-        <v>0.2524430740088508</v>
+        <v>0.14087958548077428</v>
       </c>
       <c r="L16" s="234">
-        <v>0.14087958548077428</v>
+        <v>0.12183614217621064</v>
       </c>
       <c r="M16" s="202"/>
       <c r="N16" s="232">
-        <v>7.5091312934923398</v>
+        <v>0.23471336839141776</v>
       </c>
       <c r="O16" s="234">
-        <v>1.2671673680044098</v>
+        <v>0.21616374545680617</v>
       </c>
       <c r="P16" s="258"/>
       <c r="Q16" s="229"/>
@@ -26569,20 +26570,20 @@
         <v>80</v>
       </c>
       <c r="J17" s="121">
-        <v>2442.7443873500001</v>
+        <v>1894.29237844</v>
       </c>
       <c r="K17" s="122">
-        <v>1894.29237844</v>
+        <v>2109.6194610500002</v>
       </c>
       <c r="L17" s="123">
-        <v>2109.6194610500002</v>
+        <v>1722.1210796</v>
       </c>
       <c r="M17" s="75"/>
       <c r="N17" s="121">
-        <v>16480.22902545</v>
+        <v>2225.0074729399998</v>
       </c>
       <c r="O17" s="123">
-        <v>31229.205453959999</v>
+        <v>18696.104981050001</v>
       </c>
       <c r="P17" s="261"/>
       <c r="Q17" s="229"/>
@@ -26606,20 +26607,20 @@
       <c r="H18" s="122"/>
       <c r="I18" s="1118"/>
       <c r="J18" s="121">
-        <v>2997.16455438</v>
+        <v>3367.47669038</v>
       </c>
       <c r="K18" s="122">
-        <v>3367.47669038</v>
+        <v>3062.02803047</v>
       </c>
       <c r="L18" s="123">
-        <v>3062.02803047</v>
+        <v>3304.0111476699999</v>
       </c>
       <c r="M18" s="75"/>
       <c r="N18" s="121">
-        <v>22206.062888460001</v>
+        <v>3495.3086535500001</v>
       </c>
       <c r="O18" s="123">
-        <v>41110.690730479997</v>
+        <v>25703.947643240001</v>
       </c>
       <c r="P18" s="261"/>
       <c r="Q18" s="229"/>
@@ -26643,20 +26644,20 @@
       <c r="H19" s="122"/>
       <c r="I19" s="1118"/>
       <c r="J19" s="121">
-        <v>2362.47071951</v>
+        <v>2416.9668335400002</v>
       </c>
       <c r="K19" s="122">
-        <v>2416.9668335400002</v>
+        <v>2154.6607888600001</v>
       </c>
       <c r="L19" s="123">
-        <v>2154.6607888600001</v>
+        <v>2342.1373174099999</v>
       </c>
       <c r="M19" s="75"/>
       <c r="N19" s="121">
-        <v>17894.47491017</v>
+        <v>2534.28285353</v>
       </c>
       <c r="O19" s="123">
-        <v>33432.704112759995</v>
+        <v>20414.649373529999</v>
       </c>
       <c r="P19" s="261"/>
       <c r="Q19" s="229"/>
@@ -26680,20 +26681,20 @@
       <c r="H20" s="122"/>
       <c r="I20" s="1118"/>
       <c r="J20" s="121">
-        <v>1775.4407203000001</v>
+        <v>1433.1139043799999</v>
       </c>
       <c r="K20" s="122">
-        <v>1433.1139043799999</v>
+        <v>1527.5512530799999</v>
       </c>
       <c r="L20" s="123">
-        <v>1527.5512530799999</v>
+        <v>1497.6152210400001</v>
       </c>
       <c r="M20" s="75"/>
       <c r="N20" s="121">
-        <v>10667.001961600001</v>
+        <v>1781.3762079999999</v>
       </c>
       <c r="O20" s="123">
-        <v>19840.354775390002</v>
+        <v>12452.34424283</v>
       </c>
       <c r="P20" s="261"/>
       <c r="Q20" s="229"/>
@@ -26740,20 +26741,20 @@
         <v>80</v>
       </c>
       <c r="J22" s="129">
-        <v>6128.0264597900004</v>
+        <v>6876.66162343</v>
       </c>
       <c r="K22" s="130">
-        <v>6876.66162343</v>
+        <v>6755.7314468200002</v>
       </c>
       <c r="L22" s="131">
-        <v>6755.7314468200002</v>
+        <v>6706.5929163800001</v>
       </c>
       <c r="M22" s="202"/>
       <c r="N22" s="129">
-        <v>6695.9916438600003</v>
+        <v>7059.5011781399999</v>
       </c>
       <c r="O22" s="131">
-        <v>48998.690205259998</v>
+        <v>56068.792655920006</v>
       </c>
       <c r="P22" s="258"/>
       <c r="Q22" s="229"/>
@@ -26779,20 +26780,20 @@
         <v>67</v>
       </c>
       <c r="J23" s="232">
-        <v>-5.5478608661126638E-2</v>
+        <v>7.5165456458021973E-2</v>
       </c>
       <c r="K23" s="233">
-        <v>7.5165456458021973E-2</v>
+        <v>-1.4290180255196239E-2</v>
       </c>
       <c r="L23" s="234">
-        <v>-1.4290180255196239E-2</v>
+        <v>3.7735224242906762E-2</v>
       </c>
       <c r="M23" s="202"/>
       <c r="N23" s="232">
-        <v>3.6094851246816217E-2</v>
+        <v>-1.8304803327339969E-2</v>
       </c>
       <c r="O23" s="234">
-        <v>-2.5795771718869043E-2</v>
+        <v>-2.4674308697898328E-2</v>
       </c>
       <c r="P23" s="258"/>
       <c r="Q23" s="229"/>
@@ -26820,20 +26821,20 @@
         <v>80</v>
       </c>
       <c r="J24" s="121">
-        <v>1162.43639545</v>
+        <v>1119.19437406</v>
       </c>
       <c r="K24" s="122">
-        <v>1119.19437406</v>
+        <v>1167.16911031</v>
       </c>
       <c r="L24" s="123">
-        <v>1167.16911031</v>
+        <v>1310.2484227899999</v>
       </c>
       <c r="M24" s="264"/>
       <c r="N24" s="121">
-        <v>1310.2484227899999</v>
+        <v>1412.94943691</v>
       </c>
       <c r="O24" s="123">
-        <v>9276.8012137000005</v>
+        <v>10689.75065061</v>
       </c>
       <c r="P24" s="261"/>
       <c r="Q24" s="229"/>
@@ -26857,20 +26858,20 @@
       <c r="H25" s="122"/>
       <c r="I25" s="1118"/>
       <c r="J25" s="121">
-        <v>2246.5179058399999</v>
+        <v>2343.5812234599998</v>
       </c>
       <c r="K25" s="122">
-        <v>2343.5812234599998</v>
+        <v>2425.85753858</v>
       </c>
       <c r="L25" s="123">
-        <v>2425.85753858</v>
+        <v>2235.13030162</v>
       </c>
       <c r="M25" s="264"/>
       <c r="N25" s="121">
-        <v>2235.1346361000001</v>
+        <v>2520.9839229700001</v>
       </c>
       <c r="O25" s="123">
-        <v>16949.051997630002</v>
+        <v>19470.03158612</v>
       </c>
       <c r="P25" s="261"/>
       <c r="Q25" s="229"/>
@@ -26894,20 +26895,20 @@
       <c r="H26" s="122"/>
       <c r="I26" s="1118"/>
       <c r="J26" s="121">
-        <v>297.44459426999998</v>
+        <v>810.01359132000005</v>
       </c>
       <c r="K26" s="122">
-        <v>810.01359132000005</v>
+        <v>630.69778924000002</v>
       </c>
       <c r="L26" s="123">
-        <v>630.69778924000002</v>
+        <v>527.80123150999998</v>
       </c>
       <c r="M26" s="264"/>
       <c r="N26" s="121">
-        <v>517.19562451000002</v>
+        <v>181.43020468</v>
       </c>
       <c r="O26" s="123">
-        <v>2832.5070699500002</v>
+        <v>3024.54288163</v>
       </c>
       <c r="P26" s="261"/>
       <c r="Q26" s="229"/>
@@ -26931,20 +26932,20 @@
       <c r="H27" s="122"/>
       <c r="I27" s="1118"/>
       <c r="J27" s="121">
-        <v>1034.7996693600001</v>
+        <v>1094.30052077</v>
       </c>
       <c r="K27" s="122">
-        <v>1094.30052077</v>
+        <v>1082.7676478000001</v>
       </c>
       <c r="L27" s="123">
-        <v>1082.7676478000001</v>
+        <v>1159.45995103</v>
       </c>
       <c r="M27" s="264"/>
       <c r="N27" s="121">
-        <v>1159.45995103</v>
+        <v>1255.54830077</v>
       </c>
       <c r="O27" s="123">
-        <v>8386.5318090199999</v>
+        <v>9642.0801097900003</v>
       </c>
       <c r="P27" s="261"/>
       <c r="Q27" s="229"/>
@@ -26968,20 +26969,20 @@
       <c r="H28" s="122"/>
       <c r="I28" s="1118"/>
       <c r="J28" s="121">
-        <v>878.91909126999997</v>
+        <v>922.77744569000004</v>
       </c>
       <c r="K28" s="122">
-        <v>922.77744569000004</v>
+        <v>889.07783347999998</v>
       </c>
       <c r="L28" s="123">
-        <v>889.07783347999998</v>
+        <v>941.43059075999997</v>
       </c>
       <c r="M28" s="264"/>
       <c r="N28" s="121">
-        <v>941.43059075999997</v>
+        <v>1128.8994365999999</v>
       </c>
       <c r="O28" s="123">
-        <v>7192.7584739699996</v>
+        <v>8321.6579105700002</v>
       </c>
       <c r="P28" s="261"/>
       <c r="Q28" s="229"/>
@@ -27005,20 +27006,20 @@
       <c r="H29" s="122"/>
       <c r="I29" s="1118"/>
       <c r="J29" s="121">
-        <v>389.45707413000002</v>
+        <v>455.40716743000002</v>
       </c>
       <c r="K29" s="122">
-        <v>455.40716743000002</v>
+        <v>448.00559944999998</v>
       </c>
       <c r="L29" s="123">
-        <v>448.00559944999998</v>
+        <v>423.36605300000002</v>
       </c>
       <c r="M29" s="264"/>
       <c r="N29" s="121">
-        <v>423.36605300000002</v>
+        <v>450.09184613999997</v>
       </c>
       <c r="O29" s="123">
-        <v>3468.9390560099996</v>
+        <v>3919.0309021499997</v>
       </c>
       <c r="P29" s="261"/>
       <c r="Q29" s="229"/>
@@ -27042,20 +27043,20 @@
       <c r="H30" s="122"/>
       <c r="I30" s="1118"/>
       <c r="J30" s="121">
-        <v>118.45172947</v>
+        <v>131.3873007</v>
       </c>
       <c r="K30" s="122">
-        <v>131.3873007</v>
+        <v>112.15592796</v>
       </c>
       <c r="L30" s="123">
-        <v>112.15592796</v>
+        <v>109.15636567</v>
       </c>
       <c r="M30" s="264"/>
       <c r="N30" s="121">
-        <v>109.15636567</v>
+        <v>109.59803006999999</v>
       </c>
       <c r="O30" s="123">
-        <v>892.10058498000001</v>
+        <v>1001.6986150499999</v>
       </c>
       <c r="P30" s="261"/>
       <c r="Q30" s="229"/>
@@ -27102,20 +27103,20 @@
         <v>80</v>
       </c>
       <c r="J32" s="129">
-        <v>3449.7939217499988</v>
+        <v>2235.1881833099997</v>
       </c>
       <c r="K32" s="130">
-        <v>2235.1881833099997</v>
+        <v>2098.1280866399993</v>
       </c>
       <c r="L32" s="131">
-        <v>2098.1280866399993</v>
+        <v>2159.2918493400002</v>
       </c>
       <c r="M32" s="202"/>
       <c r="N32" s="129">
-        <v>60551.777141820006</v>
+        <v>2976.4740098800003</v>
       </c>
       <c r="O32" s="131">
-        <v>76614.264867329999</v>
+        <v>21198.253584729995</v>
       </c>
       <c r="P32" s="258"/>
       <c r="Q32" s="229"/>
@@ -27139,20 +27140,20 @@
       <c r="H33" s="130"/>
       <c r="I33" s="1125"/>
       <c r="J33" s="265">
-        <v>15705.84684133</v>
+        <v>15988.51143017</v>
       </c>
       <c r="K33" s="266">
-        <v>15988.51143017</v>
+        <v>15609.59098028</v>
       </c>
       <c r="L33" s="267">
-        <v>15609.59098028</v>
+        <v>15572.477682100001</v>
       </c>
       <c r="M33" s="202"/>
       <c r="N33" s="129">
-        <v>73943.760429540009</v>
+        <v>17095.476366160001</v>
       </c>
       <c r="O33" s="131">
-        <v>174611.64527785001</v>
+        <v>133335.83889657</v>
       </c>
       <c r="P33" s="258"/>
       <c r="Q33" s="229"/>
@@ -29092,8 +29093,8 @@
     <mergeCell ref="N78:O78"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{D836DDB6-9073-4310-B947-01643B803D9B}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{B80F4A71-E850-42C6-96AF-F642A65816B9}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{927B9CF9-5CB8-494D-B2C4-0E45822E763B}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{1BDEC147-CCED-4BE1-A49C-70605022F297}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="37" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -29102,7 +29103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3358EB73-CC42-487B-B1BB-3DDC6657D62D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEDF352-80C7-4040-B384-1D19FDFC1776}">
   <sheetPr codeName="Hoja9">
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="1"/>
@@ -32456,8 +32457,8 @@
     <mergeCell ref="I73:I79"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{4A7C5F9A-A524-4B81-8C50-A8D60B3CEFEC}"/>
-    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{C00B9373-B20E-4EF8-B902-1CC53B8B51D6}"/>
+    <hyperlink ref="F2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{AE8AA1E6-7E03-4C82-B76E-910312E60D8B}"/>
+    <hyperlink ref="J2" location="Fuentes!A1" display="Fuentes" xr:uid="{2E30B0E6-FE55-435B-87E9-DF16E3719E41}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.98425196850393704" bottom="0.39370078740157483" header="0.59055118110236227" footer="1.1811023622047245"/>
   <pageSetup scale="41" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -32466,7 +32467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB3043D-4681-4DDB-8439-949F03579560}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C531A2AF-4036-4194-AF35-B89B37DFD4E7}">
   <sheetPr codeName="Hoja10">
     <tabColor theme="3" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
@@ -32939,29 +32940,29 @@
     <mergeCell ref="C32:C33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F13" r:id="rId1" xr:uid="{60225A68-8831-447F-9718-1BAD2BDE78F7}"/>
-    <hyperlink ref="F14" r:id="rId2" xr:uid="{13DD9A54-A222-4C70-A0F8-44FE3B41EC34}"/>
-    <hyperlink ref="F15" r:id="rId3" xr:uid="{1D131B35-D77C-447E-8FD9-580DC20936D3}"/>
-    <hyperlink ref="F16" r:id="rId4" xr:uid="{0A98C992-976E-45D0-9E46-89019A188ED3}"/>
-    <hyperlink ref="F17" r:id="rId5" xr:uid="{091F3BC2-1EF0-4449-96D6-822240958A61}"/>
-    <hyperlink ref="F18" r:id="rId6" xr:uid="{48A9747D-DF76-4D9A-85BB-68432EC3DCB9}"/>
-    <hyperlink ref="F20" r:id="rId7" xr:uid="{9A59B39E-A4F9-4D80-A497-3F55ABEB34CE}"/>
-    <hyperlink ref="F22" r:id="rId8" xr:uid="{A7406B72-2D78-469D-A16A-243878B971D9}"/>
-    <hyperlink ref="F21" r:id="rId9" xr:uid="{AAA9222D-A2A1-4874-AC0B-8E18D786FF46}"/>
-    <hyperlink ref="F23" r:id="rId10" xr:uid="{AA2C6523-0633-4B6D-A409-A20755831425}"/>
-    <hyperlink ref="F25" r:id="rId11" xr:uid="{B025FD4A-4F66-43AB-B1AA-025B49225A24}"/>
-    <hyperlink ref="F27" r:id="rId12" xr:uid="{5E76D779-A2C6-4826-B326-3A655008B9EB}"/>
-    <hyperlink ref="F30" r:id="rId13" xr:uid="{55ACE434-4088-4FE1-B3AF-5ABA91ADEB5A}"/>
-    <hyperlink ref="F33" r:id="rId14" xr:uid="{43138ECC-6336-4BB8-B130-1119E27D52A5}"/>
-    <hyperlink ref="F32" r:id="rId15" xr:uid="{8092A83E-148E-42A3-8D31-017C807CDC6A}"/>
-    <hyperlink ref="F35" r:id="rId16" xr:uid="{1179D9DD-727C-4880-8A4A-1B06B63FF0D4}"/>
-    <hyperlink ref="F36" r:id="rId17" xr:uid="{BA2A1AA1-4226-4A9A-A1C4-8789CA033BAE}"/>
-    <hyperlink ref="F37" r:id="rId18" xr:uid="{536826B4-F7A0-423A-ADAA-7934E636D264}"/>
-    <hyperlink ref="F38" r:id="rId19" xr:uid="{A71DE205-7006-475A-8FB7-64C4A2FE714F}"/>
-    <hyperlink ref="F39" r:id="rId20" xr:uid="{7D0524CF-E6D7-4C43-A931-05E481AF1E59}"/>
-    <hyperlink ref="F41" r:id="rId21" xr:uid="{EDED8362-AF3A-430A-B5D4-AAED54189095}"/>
-    <hyperlink ref="C2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{67AC8827-C2AE-4990-9FF6-D7E73F610316}"/>
-    <hyperlink ref="F28" r:id="rId22" xr:uid="{6105B80F-EA05-4F93-94A7-ED75328E077B}"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{CA8EE1A6-DEA5-43BB-B276-B23960B40142}"/>
+    <hyperlink ref="F14" r:id="rId2" xr:uid="{BDAE9601-0DE5-4399-A9F4-AC6E999D478A}"/>
+    <hyperlink ref="F15" r:id="rId3" xr:uid="{8C86AFB4-19D9-4D04-9E8B-E4D4CD7EE7F9}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{420DDCB2-37FC-4B9B-99D8-908F5227D3BF}"/>
+    <hyperlink ref="F17" r:id="rId5" xr:uid="{059A4B84-D71D-488D-97B8-638C3C91C7B9}"/>
+    <hyperlink ref="F18" r:id="rId6" xr:uid="{3CC1D936-C4AA-4EBD-B151-20142C360196}"/>
+    <hyperlink ref="F20" r:id="rId7" xr:uid="{70450D9A-56D6-4221-87D0-D3EBAE62FA7F}"/>
+    <hyperlink ref="F22" r:id="rId8" xr:uid="{1D9FCB44-147D-4126-B9C0-78E528AF160B}"/>
+    <hyperlink ref="F21" r:id="rId9" xr:uid="{5A347904-B2A7-4368-AB41-9D7BE88E7868}"/>
+    <hyperlink ref="F23" r:id="rId10" xr:uid="{ED282389-64C3-48AA-ABE9-F22A27EFCF79}"/>
+    <hyperlink ref="F25" r:id="rId11" xr:uid="{92E0AF8C-9209-4815-9C07-417F225A16B3}"/>
+    <hyperlink ref="F27" r:id="rId12" xr:uid="{D6682460-F1AF-4271-A885-F6D87FE4192E}"/>
+    <hyperlink ref="F30" r:id="rId13" xr:uid="{8885CE76-A9D6-4CF5-BCFC-E77BACF54327}"/>
+    <hyperlink ref="F33" r:id="rId14" xr:uid="{77B4B7BB-8C78-4C99-8FCA-E01DE50BE544}"/>
+    <hyperlink ref="F32" r:id="rId15" xr:uid="{6C442815-FFAE-49C9-A912-090A4A388FA4}"/>
+    <hyperlink ref="F35" r:id="rId16" xr:uid="{556BE462-DFFF-421B-9085-714D7E665279}"/>
+    <hyperlink ref="F36" r:id="rId17" xr:uid="{1A33C59C-2630-4F24-BC74-7A75A344BB2F}"/>
+    <hyperlink ref="F37" r:id="rId18" xr:uid="{26854B1D-10DE-4D5B-8065-8715E62B497B}"/>
+    <hyperlink ref="F38" r:id="rId19" xr:uid="{BF13B6DC-68AB-438D-AE9B-F6727D8254E9}"/>
+    <hyperlink ref="F39" r:id="rId20" xr:uid="{E327920A-B7BD-4BE1-BF36-EE0846F61826}"/>
+    <hyperlink ref="F41" r:id="rId21" xr:uid="{F1284AC1-5756-4030-A0BA-48AF77CFB7D8}"/>
+    <hyperlink ref="C2" location="'Principales Indicadores'!A1" display="Principales indicadores" xr:uid="{C06E483C-1619-4F3C-A033-77AF313A6499}"/>
+    <hyperlink ref="F28" r:id="rId22" xr:uid="{2DB45012-C2ED-4CA0-8840-EF0B4C87C8CD}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="1.1811023622047245" bottom="0.39370078740157483" header="1.5748031496062993" footer="1.1811023622047245"/>
   <pageSetup scale="44" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId23"/>
